--- a/backend/uploads/reconciled_verified_donations.xlsx
+++ b/backend/uploads/reconciled_verified_donations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +453,426 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-23 at 10.34.57 (1).jpeg</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>file.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>317017653200</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2501</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>RAISE INDIA FOUNDATI</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MATCHED &amp; VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-23 at 10.34.57.jpeg</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>file.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>049458478888</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RAISE INDIA FOUNDATI</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MATCHED &amp; VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-23 at 10.34.56 (1).jpeg</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>file.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>110931485407</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>500</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>RAISE INDIA FOUNDATI</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MATCHED &amp; VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-23 at 10.34.56.jpeg</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>file.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>643620935985</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>RAISE INDIA FOUNDATI</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MATCHED &amp; VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-23 at 10.34.55.jpeg</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>file.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>317016312168</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RAISE INDIA FOUNDATI</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MATCHED &amp; VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-23 at 10.34.53 (3).jpeg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>file.xlsx</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>078038536939</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>RAISE INDIA FOUNDATI</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MATCHED &amp; VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-23 at 10.34.53 (1).jpeg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>file.xlsx</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>110931400126</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>RAISE INDIA FOUNDATI</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MATCHED &amp; VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-23 at 10.34.53.jpeg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>file.xlsx</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>110931400126</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>500</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>RAISE INDIA FOUNDATI</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MATCHED &amp; VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-23 at 10.34.52 (2).jpeg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>file.xlsx</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>724697755884</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>RAISE INDIA FOUNDATI</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MATCHED &amp; VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-23 at 10.34.52.jpeg</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>file.xlsx</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>431699183107</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>501</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>RAISE INDIA FOUNDATI</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MATCHED &amp; VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-23 at 10.34.51 (1).jpeg</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>file.xlsx</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>876716697478</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>RAISE INDIA FOUNDATI</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MATCHED &amp; VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-23 at 10.34.51.jpeg</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>file.xlsx</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>628936748605</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>764</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>RAISE INDIA FOUNDATI</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MATCHED &amp; VERIFIED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
